--- a/입주율.xlsx
+++ b/입주율.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\user\Desktop\0. 마케팅기획팀\2026\0. 스터디\2026\streamlit_study\입주율\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CD8409B3-073C-4FA0-8627-9F432D5B0208}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3D3763EA-7B50-4499-9749-789E8E1369B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0A7804FE-602F-43C7-89D4-5BC7C0FE7964}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F84EA87C-4766-42D5-B851-61535546FEAF}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -1971,7 +1971,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F44A7645-290D-4C3A-AD55-2ABF9D6FB0D9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26C43CCE-87E2-4012-9D8A-398A1F9FB0E7}">
   <dimension ref="A1:BB271"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -2782,10 +2782,10 @@
         <v>44935</v>
       </c>
       <c r="E12">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="F12" s="2">
-        <v>0.97970000000000002</v>
+        <v>0.98150000000000004</v>
       </c>
       <c r="I12">
         <v>27</v>
@@ -2876,6 +2876,9 @@
       </c>
       <c r="AW12">
         <v>1</v>
+      </c>
+      <c r="AX12">
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:54" x14ac:dyDescent="0.3">
@@ -3880,10 +3883,10 @@
         <v>45930</v>
       </c>
       <c r="E27">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="F27" s="2">
-        <v>0.6925</v>
+        <v>0.69879999999999998</v>
       </c>
       <c r="I27">
         <v>36</v>
@@ -3913,7 +3916,7 @@
         <v>12</v>
       </c>
       <c r="R27">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:53" x14ac:dyDescent="0.3">
@@ -3930,10 +3933,10 @@
         <v>46085</v>
       </c>
       <c r="E28">
-        <v>389</v>
+        <v>402</v>
       </c>
       <c r="F28" s="2">
-        <v>0.71640000000000004</v>
+        <v>0.74029999999999996</v>
       </c>
       <c r="H28">
         <v>65</v>
@@ -3948,7 +3951,7 @@
         <v>66</v>
       </c>
       <c r="L28">
-        <v>22</v>
+        <v>35</v>
       </c>
     </row>
     <row r="29" spans="1:53" x14ac:dyDescent="0.3">
@@ -5906,10 +5909,10 @@
         <v>45694</v>
       </c>
       <c r="E59">
-        <v>714</v>
+        <v>724</v>
       </c>
       <c r="F59" s="2">
-        <v>0.85299999999999998</v>
+        <v>0.86499999999999999</v>
       </c>
       <c r="L59">
         <v>53</v>
@@ -5951,7 +5954,7 @@
         <v>63</v>
       </c>
       <c r="Y59">
-        <v>18</v>
+        <v>28</v>
       </c>
     </row>
     <row r="60" spans="1:43" x14ac:dyDescent="0.3">
@@ -6107,10 +6110,10 @@
         <v>45498</v>
       </c>
       <c r="E62">
-        <v>740</v>
+        <v>744</v>
       </c>
       <c r="F62" s="2">
-        <v>0.93200000000000005</v>
+        <v>0.93700000000000006</v>
       </c>
       <c r="G62">
         <v>4</v>
@@ -6188,7 +6191,7 @@
         <v>8</v>
       </c>
       <c r="AF62">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="63" spans="1:43" x14ac:dyDescent="0.3">
@@ -6205,10 +6208,10 @@
         <v>45762</v>
       </c>
       <c r="E63">
-        <v>547</v>
+        <v>559</v>
       </c>
       <c r="F63" s="2">
-        <v>0.9012</v>
+        <v>0.92090000000000005</v>
       </c>
       <c r="G63">
         <v>1</v>
@@ -6253,7 +6256,7 @@
         <v>26</v>
       </c>
       <c r="W63">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="64" spans="1:43" x14ac:dyDescent="0.3">
@@ -6270,10 +6273,10 @@
         <v>45877</v>
       </c>
       <c r="E64">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="F64" s="2">
-        <v>0.37459999999999999</v>
+        <v>0.38340000000000002</v>
       </c>
       <c r="I64">
         <v>54</v>
@@ -6306,7 +6309,7 @@
         <v>5</v>
       </c>
       <c r="S64">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="65" spans="1:50" x14ac:dyDescent="0.3">
@@ -7482,10 +7485,10 @@
         <v>44985</v>
       </c>
       <c r="E82">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="F82" s="2">
-        <v>0.97609999999999997</v>
+        <v>0.97770000000000001</v>
       </c>
       <c r="H82">
         <v>43</v>
@@ -7572,7 +7575,7 @@
         <v>4</v>
       </c>
       <c r="AW82">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83" spans="1:51" x14ac:dyDescent="0.3">
@@ -8113,10 +8116,10 @@
         <v>45253</v>
       </c>
       <c r="E90">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F90" s="2">
-        <v>0.38540000000000002</v>
+        <v>0.39579999999999999</v>
       </c>
       <c r="K90">
         <v>1</v>
@@ -8180,6 +8183,9 @@
       </c>
       <c r="AM90">
         <v>2</v>
+      </c>
+      <c r="AN90">
+        <v>1</v>
       </c>
     </row>
     <row r="91" spans="1:51" x14ac:dyDescent="0.3">
@@ -8385,10 +8391,10 @@
         <v>46148</v>
       </c>
       <c r="E94">
-        <v>162</v>
+        <v>181</v>
       </c>
       <c r="F94" s="2">
-        <v>0.2344</v>
+        <v>0.26190000000000002</v>
       </c>
       <c r="H94">
         <v>10</v>
@@ -8397,7 +8403,7 @@
         <v>120</v>
       </c>
       <c r="J94">
-        <v>32</v>
+        <v>51</v>
       </c>
     </row>
     <row r="95" spans="1:51" x14ac:dyDescent="0.3">
@@ -8414,10 +8420,10 @@
         <v>46006</v>
       </c>
       <c r="E95">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="F95" s="2">
-        <v>0.22339999999999999</v>
+        <v>0.23799999999999999</v>
       </c>
       <c r="H95">
         <v>1</v>
@@ -8441,7 +8447,7 @@
         <v>46</v>
       </c>
       <c r="O95">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="96" spans="1:51" x14ac:dyDescent="0.3">
@@ -8600,10 +8606,10 @@
         <v>45950</v>
       </c>
       <c r="E98">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F98" s="2">
-        <v>0.60680000000000001</v>
+        <v>0.60870000000000002</v>
       </c>
       <c r="I98">
         <v>2</v>
@@ -8630,7 +8636,7 @@
         <v>23</v>
       </c>
       <c r="Q98">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="99" spans="1:53" x14ac:dyDescent="0.3">
@@ -8824,10 +8830,10 @@
         <v>45602</v>
       </c>
       <c r="E102">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="F102" s="2">
-        <v>0.87339999999999995</v>
+        <v>0.8821</v>
       </c>
       <c r="H102">
         <v>1</v>
@@ -8885,6 +8891,9 @@
       </c>
       <c r="AA102">
         <v>3</v>
+      </c>
+      <c r="AB102">
+        <v>2</v>
       </c>
     </row>
     <row r="103" spans="1:53" x14ac:dyDescent="0.3">
@@ -8901,10 +8910,10 @@
         <v>45623</v>
       </c>
       <c r="E103">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="F103" s="2">
-        <v>0.96350000000000002</v>
+        <v>0.96699999999999997</v>
       </c>
       <c r="I103">
         <v>7</v>
@@ -8955,7 +8964,7 @@
         <v>1</v>
       </c>
       <c r="AB103">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="104" spans="1:53" x14ac:dyDescent="0.3">
@@ -10263,10 +10272,10 @@
         <v>46007</v>
       </c>
       <c r="E121">
-        <v>1847</v>
+        <v>1871</v>
       </c>
       <c r="F121" s="2">
-        <v>0.91300000000000003</v>
+        <v>0.92490000000000006</v>
       </c>
       <c r="K121">
         <v>173</v>
@@ -10281,7 +10290,7 @@
         <v>255</v>
       </c>
       <c r="O121">
-        <v>61</v>
+        <v>85</v>
       </c>
     </row>
     <row r="122" spans="1:54" x14ac:dyDescent="0.3">
@@ -10298,10 +10307,10 @@
         <v>46000</v>
       </c>
       <c r="E122">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="F122" s="2">
-        <v>0.15920000000000001</v>
+        <v>0.17649999999999999</v>
       </c>
       <c r="K122">
         <v>4</v>
@@ -10316,7 +10325,7 @@
         <v>15</v>
       </c>
       <c r="O122">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="123" spans="1:54" x14ac:dyDescent="0.3">
@@ -12720,10 +12729,10 @@
         <v>45840</v>
       </c>
       <c r="E157">
-        <v>292</v>
+        <v>306</v>
       </c>
       <c r="F157" s="2">
-        <v>0.64890000000000003</v>
+        <v>0.68</v>
       </c>
       <c r="J157">
         <v>11</v>
@@ -12756,7 +12765,7 @@
         <v>34</v>
       </c>
       <c r="T157">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="158" spans="1:53" x14ac:dyDescent="0.3">
@@ -12811,10 +12820,10 @@
         <v>45680</v>
       </c>
       <c r="E159">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="F159" s="2">
-        <v>0.96040000000000003</v>
+        <v>0.96240000000000003</v>
       </c>
       <c r="J159">
         <v>101</v>
@@ -12859,6 +12868,9 @@
         <v>2</v>
       </c>
       <c r="Y159">
+        <v>1</v>
+      </c>
+      <c r="Z159">
         <v>1</v>
       </c>
     </row>
@@ -12982,10 +12994,10 @@
         <v>45478</v>
       </c>
       <c r="E162">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F162" s="2">
-        <v>0.97440000000000004</v>
+        <v>1</v>
       </c>
       <c r="H162">
         <v>3</v>
@@ -13039,6 +13051,9 @@
         <v>2</v>
       </c>
       <c r="AE162">
+        <v>1</v>
+      </c>
+      <c r="AF162">
         <v>1</v>
       </c>
     </row>
@@ -13139,10 +13154,10 @@
         <v>45915</v>
       </c>
       <c r="E164">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F164" s="2">
-        <v>0.315</v>
+        <v>0.31909999999999999</v>
       </c>
       <c r="K164">
         <v>2</v>
@@ -13166,7 +13181,7 @@
         <v>12</v>
       </c>
       <c r="R164">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="165" spans="1:50" x14ac:dyDescent="0.3">
@@ -13268,10 +13283,10 @@
         <v>45569</v>
       </c>
       <c r="E167">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F167" s="2">
-        <v>0.55279999999999996</v>
+        <v>0.56100000000000005</v>
       </c>
       <c r="Q167">
         <v>1</v>
@@ -13310,7 +13325,7 @@
         <v>4</v>
       </c>
       <c r="AC167">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="168" spans="1:50" x14ac:dyDescent="0.3">
@@ -13525,10 +13540,10 @@
         <v>45366</v>
       </c>
       <c r="E171">
-        <v>35</v>
+        <v>91</v>
       </c>
       <c r="F171" s="2">
-        <v>3.5400000000000001E-2</v>
+        <v>9.1899999999999996E-2</v>
       </c>
       <c r="O171">
         <v>4</v>
@@ -13537,7 +13552,7 @@
         <v>8</v>
       </c>
       <c r="AJ171">
-        <v>23</v>
+        <v>79</v>
       </c>
     </row>
     <row r="172" spans="1:50" x14ac:dyDescent="0.3">
@@ -14168,10 +14183,10 @@
         <v>45232</v>
       </c>
       <c r="E182">
-        <v>949</v>
+        <v>951</v>
       </c>
       <c r="F182" s="2">
-        <v>0.99580000000000002</v>
+        <v>0.99790000000000001</v>
       </c>
       <c r="G182">
         <v>30</v>
@@ -14240,7 +14255,7 @@
         <v>1</v>
       </c>
       <c r="AN182">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="183" spans="1:51" x14ac:dyDescent="0.3">
@@ -15402,10 +15417,10 @@
         <v>45974</v>
       </c>
       <c r="E199">
-        <v>1619</v>
+        <v>1620</v>
       </c>
       <c r="F199" s="2">
-        <v>0.92090000000000005</v>
+        <v>0.92149999999999999</v>
       </c>
       <c r="I199">
         <v>711</v>
@@ -15429,7 +15444,7 @@
         <v>14</v>
       </c>
       <c r="P199">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="200" spans="1:54" x14ac:dyDescent="0.3">
@@ -15446,10 +15461,10 @@
         <v>45736</v>
       </c>
       <c r="E200">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="F200" s="2">
-        <v>0.58120000000000005</v>
+        <v>0.58689999999999998</v>
       </c>
       <c r="K200">
         <v>6</v>
@@ -15491,7 +15506,7 @@
         <v>13</v>
       </c>
       <c r="X200">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="201" spans="1:54" x14ac:dyDescent="0.3">
@@ -15508,10 +15523,10 @@
         <v>45987</v>
       </c>
       <c r="E201">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="F201" s="2">
-        <v>0.37890000000000001</v>
+        <v>0.38369999999999999</v>
       </c>
       <c r="J201">
         <v>18</v>
@@ -15532,7 +15547,7 @@
         <v>20</v>
       </c>
       <c r="P201">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="202" spans="1:54" x14ac:dyDescent="0.3">
@@ -16321,10 +16336,10 @@
         <v>45226</v>
       </c>
       <c r="E213">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F213" s="2">
-        <v>0.51180000000000003</v>
+        <v>0.51759999999999995</v>
       </c>
       <c r="G213">
         <v>1</v>
@@ -16421,6 +16436,9 @@
       </c>
       <c r="AN213">
         <v>5</v>
+      </c>
+      <c r="AO213">
+        <v>1</v>
       </c>
     </row>
     <row r="214" spans="1:52" x14ac:dyDescent="0.3">
@@ -16886,10 +16904,10 @@
         <v>45359</v>
       </c>
       <c r="E221">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F221" s="2">
-        <v>0.84550000000000003</v>
+        <v>0.84960000000000002</v>
       </c>
       <c r="I221">
         <v>31</v>
@@ -16970,7 +16988,7 @@
         <v>1</v>
       </c>
       <c r="AJ221">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="222" spans="1:52" x14ac:dyDescent="0.3">
@@ -17333,10 +17351,10 @@
         <v>45932</v>
       </c>
       <c r="E227">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F227" s="2">
-        <v>0.95479999999999998</v>
+        <v>0.95779999999999998</v>
       </c>
       <c r="H227">
         <v>53</v>
@@ -17366,7 +17384,7 @@
         <v>1</v>
       </c>
       <c r="Q227">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="228" spans="1:45" x14ac:dyDescent="0.3">
@@ -17383,10 +17401,10 @@
         <v>45932</v>
       </c>
       <c r="E228">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F228" s="2">
-        <v>0.97470000000000001</v>
+        <v>0.98099999999999998</v>
       </c>
       <c r="H228">
         <v>22</v>
@@ -17413,6 +17431,9 @@
         <v>3</v>
       </c>
       <c r="P228">
+        <v>1</v>
+      </c>
+      <c r="Q228">
         <v>1</v>
       </c>
     </row>
@@ -17430,10 +17451,10 @@
         <v>45953</v>
       </c>
       <c r="E229">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F229" s="2">
-        <v>0.95920000000000005</v>
+        <v>0.96599999999999997</v>
       </c>
       <c r="I229">
         <v>1</v>
@@ -17460,7 +17481,7 @@
         <v>5</v>
       </c>
       <c r="Q229">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="230" spans="1:45" x14ac:dyDescent="0.3">
@@ -17477,10 +17498,10 @@
         <v>46084</v>
       </c>
       <c r="E230">
-        <v>471</v>
+        <v>482</v>
       </c>
       <c r="F230" s="2">
-        <v>0.7903</v>
+        <v>0.80869999999999997</v>
       </c>
       <c r="H230">
         <v>39</v>
@@ -17495,7 +17516,7 @@
         <v>49</v>
       </c>
       <c r="L230">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="231" spans="1:45" x14ac:dyDescent="0.3">
@@ -17512,10 +17533,10 @@
         <v>45993</v>
       </c>
       <c r="E231">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="F231" s="2">
-        <v>0.74719999999999998</v>
+        <v>0.76270000000000004</v>
       </c>
       <c r="I231">
         <v>51</v>
@@ -17536,7 +17557,7 @@
         <v>23</v>
       </c>
       <c r="O231">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="232" spans="1:45" x14ac:dyDescent="0.3">
@@ -17630,10 +17651,10 @@
         <v>45909</v>
       </c>
       <c r="E233">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="F233" s="2">
-        <v>0.5</v>
+        <v>0.50509999999999999</v>
       </c>
       <c r="I233">
         <v>16</v>
@@ -17663,7 +17684,7 @@
         <v>5</v>
       </c>
       <c r="R233">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="234" spans="1:45" x14ac:dyDescent="0.3">
@@ -19477,10 +19498,10 @@
         <v>46031</v>
       </c>
       <c r="E258">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="F258" s="2">
-        <v>0.2429</v>
+        <v>0.2455</v>
       </c>
       <c r="I258">
         <v>50</v>
@@ -19498,7 +19519,7 @@
         <v>27</v>
       </c>
       <c r="N258">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="259" spans="1:54" x14ac:dyDescent="0.3">
@@ -19597,10 +19618,10 @@
         <v>45446</v>
       </c>
       <c r="E261">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="F261" s="2">
-        <v>0.98680000000000001</v>
+        <v>0.98899999999999999</v>
       </c>
       <c r="G261">
         <v>1</v>
@@ -19673,6 +19694,9 @@
       </c>
       <c r="AF261">
         <v>4</v>
+      </c>
+      <c r="AG261">
+        <v>1</v>
       </c>
     </row>
     <row r="262" spans="1:54" x14ac:dyDescent="0.3">
@@ -19689,10 +19713,10 @@
         <v>46177</v>
       </c>
       <c r="E262">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F262" s="2">
-        <v>0.14499999999999999</v>
+        <v>0.16</v>
       </c>
       <c r="G262">
         <v>8</v>
@@ -19701,7 +19725,7 @@
         <v>17</v>
       </c>
       <c r="I262">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="263" spans="1:54" x14ac:dyDescent="0.3">
@@ -19718,10 +19742,10 @@
         <v>45567</v>
       </c>
       <c r="E263">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="F263" s="2">
-        <v>0.93830000000000002</v>
+        <v>0.94269999999999998</v>
       </c>
       <c r="I263">
         <v>6</v>
@@ -19784,7 +19808,7 @@
         <v>4</v>
       </c>
       <c r="AC263">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="264" spans="1:54" x14ac:dyDescent="0.3">
@@ -20052,10 +20076,10 @@
         <v>45652</v>
       </c>
       <c r="E268">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F268" s="2">
-        <v>0.86780000000000002</v>
+        <v>0.87929999999999997</v>
       </c>
       <c r="J268">
         <v>3</v>
@@ -20097,7 +20121,7 @@
         <v>9</v>
       </c>
       <c r="AA268">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="269" spans="1:54" x14ac:dyDescent="0.3">
@@ -20114,10 +20138,10 @@
         <v>45842</v>
       </c>
       <c r="E269">
-        <v>957</v>
+        <v>959</v>
       </c>
       <c r="F269" s="2">
-        <v>0.95220000000000005</v>
+        <v>0.95420000000000005</v>
       </c>
       <c r="G269">
         <v>1</v>
@@ -20156,6 +20180,9 @@
         <v>3</v>
       </c>
       <c r="S269">
+        <v>2</v>
+      </c>
+      <c r="T269">
         <v>2</v>
       </c>
     </row>
@@ -20238,10 +20265,10 @@
         <v>141626</v>
       </c>
       <c r="E271" s="3">
-        <v>130459</v>
+        <v>130697</v>
       </c>
       <c r="F271" s="2">
-        <v>0.92120000000000002</v>
+        <v>0.92279999999999995</v>
       </c>
       <c r="G271" s="3">
         <v>1096</v>
@@ -20250,40 +20277,40 @@
         <v>12161</v>
       </c>
       <c r="I271" s="3">
-        <v>26821</v>
+        <v>26824</v>
       </c>
       <c r="J271" s="3">
-        <v>31139</v>
+        <v>31158</v>
       </c>
       <c r="K271" s="3">
         <v>18784</v>
       </c>
       <c r="L271" s="3">
-        <v>11259</v>
+        <v>11283</v>
       </c>
       <c r="M271" s="3">
         <v>6429</v>
       </c>
       <c r="N271" s="3">
-        <v>4345</v>
+        <v>4348</v>
       </c>
       <c r="O271" s="3">
-        <v>3447</v>
+        <v>3494</v>
       </c>
       <c r="P271" s="3">
-        <v>2882</v>
+        <v>2889</v>
       </c>
       <c r="Q271" s="3">
-        <v>1516</v>
+        <v>1520</v>
       </c>
       <c r="R271" s="3">
-        <v>1297</v>
+        <v>1303</v>
       </c>
       <c r="S271" s="3">
-        <v>1375</v>
+        <v>1380</v>
       </c>
       <c r="T271" s="3">
-        <v>1501</v>
+        <v>1517</v>
       </c>
       <c r="U271">
         <v>994</v>
@@ -20292,25 +20319,25 @@
         <v>674</v>
       </c>
       <c r="W271">
-        <v>652</v>
+        <v>664</v>
       </c>
       <c r="X271">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="Y271">
-        <v>344</v>
+        <v>354</v>
       </c>
       <c r="Z271">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AA271">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AB271">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="AC271">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="AD271">
         <v>198</v>
@@ -20319,10 +20346,10 @@
         <v>127</v>
       </c>
       <c r="AF271">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="AG271">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AH271">
         <v>85</v>
@@ -20331,7 +20358,7 @@
         <v>153</v>
       </c>
       <c r="AJ271">
-        <v>71</v>
+        <v>128</v>
       </c>
       <c r="AK271">
         <v>51</v>
@@ -20343,10 +20370,10 @@
         <v>54</v>
       </c>
       <c r="AN271">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="AO271">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AP271">
         <v>25</v>
@@ -20370,10 +20397,10 @@
         <v>27</v>
       </c>
       <c r="AW271">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AX271">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AY271">
         <v>12</v>

--- a/입주율.xlsx
+++ b/입주율.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\user\Desktop\0. 마케팅기획팀\2026\0. 스터디\2026\streamlit_study\입주율\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{244FDAD0-9ABB-4F58-8813-CF8A7572E7BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5719462B-67B0-430F-B41A-72CB5503CF6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D1EE9669-BDB9-4ED5-9B34-21353F495FEB}"/>
+    <workbookView xWindow="-28920" yWindow="3900" windowWidth="29040" windowHeight="15720" xr2:uid="{D1EE9669-BDB9-4ED5-9B34-21353F495FEB}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -1971,6 +1971,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A1F7CBF-9600-409C-99F3-BE3F7DFD7B22}">
   <dimension ref="A1:BB270"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="13.5" customWidth="1"/>
+    <col min="4" max="4" width="13.5" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
